--- a/Excel1TroySpellman.xlsx
+++ b/Excel1TroySpellman.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/troyspellman/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/troyspellman/Documents/GitHub/QMBE_1320_Troy_Spellman/QMBE_1320_Troy_Spellman/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C379E0F8-BDE2-CF40-8C5F-129C0A4242AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA1B28B-DAEF-F84B-9D36-74790C8E82C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6020" yWindow="2100" windowWidth="19100" windowHeight="17440" xr2:uid="{A5426710-039F-C84D-9A19-A58B8F3D285F}"/>
+    <workbookView xWindow="6020" yWindow="840" windowWidth="19100" windowHeight="17440" xr2:uid="{A5426710-039F-C84D-9A19-A58B8F3D285F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -565,7 +565,7 @@
         <v>0.99</v>
       </c>
       <c r="F2" s="5">
-        <f>D2*E2</f>
+        <f t="shared" ref="F2:F10" si="0">D2*E2</f>
         <v>49.5</v>
       </c>
     </row>
@@ -586,7 +586,7 @@
         <v>0.99</v>
       </c>
       <c r="F3" s="5">
-        <f>D3*E3</f>
+        <f t="shared" si="0"/>
         <v>108.9</v>
       </c>
     </row>
@@ -607,7 +607,7 @@
         <v>0.99</v>
       </c>
       <c r="F4" s="5">
-        <f>D4*E4</f>
+        <f t="shared" si="0"/>
         <v>198</v>
       </c>
     </row>
@@ -628,7 +628,7 @@
         <v>0.99</v>
       </c>
       <c r="F5" s="5">
-        <f>D5*E5</f>
+        <f t="shared" si="0"/>
         <v>1386</v>
       </c>
     </row>
@@ -649,7 +649,7 @@
         <v>0.99</v>
       </c>
       <c r="F6" s="5">
-        <f>D6*E6</f>
+        <f t="shared" si="0"/>
         <v>2277</v>
       </c>
     </row>
@@ -670,7 +670,7 @@
         <v>0.99</v>
       </c>
       <c r="F7" s="5">
-        <f>D7*E7</f>
+        <f t="shared" si="0"/>
         <v>148.5</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
         <v>0.99</v>
       </c>
       <c r="F8" s="5">
-        <f>D8*E8</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>0.99</v>
       </c>
       <c r="F9" s="5">
-        <f>D9*E9</f>
+        <f t="shared" si="0"/>
         <v>74.25</v>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>0.99</v>
       </c>
       <c r="F10" s="5">
-        <f>D10*E10</f>
+        <f t="shared" si="0"/>
         <v>792</v>
       </c>
     </row>
